--- a/test.xlsx
+++ b/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mi241334\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DE39D5-8D76-4673-AFAA-4E3447F624A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB459D2-A0F9-4D77-80FC-FDA4904353F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,17 +52,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>103~109, 112~124, 133~134, 147~149</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>自室清掃*8</t>
-    <rPh sb="0" eb="4">
-      <t>ジシツセイソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>(留)補食室*4</t>
     <rPh sb="1" eb="2">
       <t>トメ</t>
@@ -135,10 +124,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>304~310, 314~315, 317~326, 329~348</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>自室清掃*?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -158,6 +143,21 @@
     <rPh sb="2" eb="4">
       <t>ヨクシツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>103~109, 112~124, 133, 134, 147~149</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自室清掃*10</t>
+    <rPh sb="0" eb="4">
+      <t>ジシツセイソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>304~310, 314, 315, 317~326, 329~348</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -494,13 +494,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.65">
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.65">
@@ -519,10 +519,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.65">
@@ -530,10 +530,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.65">
@@ -541,66 +541,66 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.65">
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.65">
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.65">
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.65">
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.65">
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mi241334\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB459D2-A0F9-4D77-80FC-FDA4904353F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD8C80B-249E-4417-8AAA-B9A0D2963A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>フロア*4</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="49">
   <si>
     <t>トイレ1期*2</t>
     <rPh sb="4" eb="5">
@@ -38,13 +34,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>トイレ2期*2</t>
-    <rPh sb="4" eb="5">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ゴミ分別*3</t>
     <rPh sb="2" eb="4">
       <t>ブンベツ</t>
@@ -65,10 +54,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>202, 204~210, 214~226, 229~246</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フロア*6</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -132,13 +117,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>階段1-4*2</t>
-    <rPh sb="0" eb="2">
-      <t>カイダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2F浴室*8</t>
     <rPh sb="2" eb="4">
       <t>ヨクシツ</t>
@@ -146,18 +124,171 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>103~109, 112~124, 133, 134, 147~149</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>自室清掃*10</t>
+    <t>111, 201, 211, 227, 247, 301, 311, 327, 401, 411, 427, 444, 501, 511, 527, 601, 611, 627, 646, 701, 707, 711, 714, 724, 727, 729, 738, 801, 805, 811, 827, 901, 911, 927</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>126, 149, 212, 249, 302, 312, 349, 402, 412, 449, 502, 549, 602, 612, 619, 634, 648, 649, 702, 712, 716, 735, 748, 749, 802, 812, 849, 902, 912, 949</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>110, 113, 125, 143, 203, 213, 228, 303, 313, 328, 403, 413, 428, 503, 513, 528, 603, 613, 628, 703, 713, 728, 803, 813, 820, 828, 903, 913, 928, 944</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>316, 534, 620, 710, 720, 744, 746, 806, 816, 821, 829, 830, 833, 843, 921, 929, 930</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>103:108, 112:124, 133, 134</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>204:210, 214:226, 229:240, 243:246, 248</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>304:310, 314, 315, 317:326, 329:348</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>404:410, 414:426, 429:443, 446:448</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 1F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 2F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 3F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 4F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 5F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 6F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 7F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 8F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 9F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>504:510, 512, 514:526, 529:533, 535:540, 543:548</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>604:610, 614:626, 628:633, 635:645, 647</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>704:706, 708, 709, 715, 717, 718, 721:723, 725, 726, 730:734, 736, 737, 739:743, 745, 747, 748</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>804, 807:810, 814, 815, 817:819, 821, 822, 824, 826, 829:832, 834:840, 844:849</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>904:910, 914:920, 922:926, 931:940, 943, 945:949</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロア*3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トイレ2期*3</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自室清掃*?</t>
     <rPh sb="0" eb="4">
       <t>ジシツセイソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>304~310, 314, 315, 317~326, 329~348</t>
+    <t>階段1-4*3</t>
+    <rPh sb="0" eb="2">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段4-7*3</t>
+    <rPh sb="0" eb="2">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C棟5階*2</t>
+    <rPh sb="1" eb="2">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段7-RF*3</t>
+    <rPh sb="0" eb="2">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\b指導寮生*?</t>
+    <rPh sb="2" eb="4">
+      <t>シドウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\b整美*?</t>
+    <rPh sb="2" eb="4">
+      <t>セイビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\b保安*?</t>
+    <rPh sb="2" eb="4">
+      <t>ホアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\b保健衛生*?</t>
+    <rPh sb="2" eb="6">
+      <t>ホケンエイセイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -201,9 +332,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,121 +620,339 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.78515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.78515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.35546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.78515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
+    <col min="12" max="13" width="11.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A4" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="E8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="F12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="F13" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="B12" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mi241334\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD8C80B-249E-4417-8AAA-B9A0D2963A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AE837D-2EEC-4BA1-8BAD-7C5227E9769F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
   <si>
     <t>トイレ1期*2</t>
     <rPh sb="4" eb="5">
@@ -156,42 +156,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t># 1F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 2F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 3F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 4F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 5F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 6F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 7F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 8F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t># 9F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>504:510, 512, 514:526, 529:533, 535:540, 543:548</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -289,6 +253,46 @@
     <rPh sb="2" eb="6">
       <t>ホケンエイセイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -623,10 +627,10 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.78515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.78515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.78515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.640625" style="1" customWidth="1"/>
@@ -639,32 +643,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.65">
@@ -693,36 +700,36 @@
         <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -780,7 +787,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.65">
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -838,7 +845,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.65">
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>7</v>
@@ -925,13 +932,13 @@
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.65">
@@ -942,7 +949,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.65">

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mi241334\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AE837D-2EEC-4BA1-8BAD-7C5227E9769F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445063F-06D0-40DA-857E-DA9C05D82176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,74 +225,74 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>\b指導寮生*?</t>
+    <t>1F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指導寮生*?</t>
+    <rPh sb="0" eb="2">
+      <t>シドウ</t>
+    </rPh>
     <rPh sb="2" eb="4">
-      <t>シドウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
       <t>リョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>\b整美*?</t>
-    <rPh sb="2" eb="4">
+    <t>整美*?</t>
+    <rPh sb="0" eb="2">
       <t>セイビ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>\b保安*?</t>
-    <rPh sb="2" eb="4">
+    <t>保安*?</t>
+    <rPh sb="0" eb="2">
       <t>ホアン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>\b保健衛生*?</t>
-    <rPh sb="2" eb="6">
+    <t>保健衛生*?</t>
+    <rPh sb="0" eb="4">
       <t>ホケンエイセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>6F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>8F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -644,34 +644,34 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.65">
@@ -717,16 +717,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
